--- a/source/bin/excel/contest.xlsx
+++ b/source/bin/excel/contest.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7747F9CE-F1F7-48AA-8632-EEDC48D79478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -66,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>kv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -79,13 +76,17 @@
   </si>
   <si>
     <t>int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -136,9 +137,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -422,7 +422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -452,7 +452,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -463,272 +463,271 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
-    <col min="14" max="17" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.75" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="7.375" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="9.25" customWidth="1"/>
+    <col min="10" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="17" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>60</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D6" s="2"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="2"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="2"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="B40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="3"/>
-      <c r="D41" s="3"/>
+      <c r="B41" s="2"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="B42" s="2"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="B43" s="2"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="2"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="2"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="2"/>
+      <c r="D46" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
